--- a/countries/hk/2026-2029.xlsx
+++ b/countries/hk/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1061,9 +1055,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1200,6 @@
       <c r="O5" t="n">
         <v>5</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -1357,9 +1345,6 @@
       <c r="O6" t="n">
         <v>15</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.2032905420295064</v>
       </c>
@@ -1505,9 +1490,6 @@
       <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -1653,9 +1635,6 @@
       <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.08131621681180255</v>
       </c>
@@ -1801,9 +1780,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1949,9 +1925,6 @@
       <c r="O10" t="n">
         <v>13</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.1761851364255722</v>
       </c>
@@ -2097,9 +2070,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2332,7 +2302,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2792,7 +2762,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -2935,9 +2905,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3083,9 +3050,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3231,9 +3195,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3379,9 +3340,6 @@
       <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -3527,9 +3485,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3675,9 +3630,6 @@
       <c r="O20" t="n">
         <v>271</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>3.672782459333082</v>
       </c>
@@ -3823,9 +3775,6 @@
       <c r="O21" t="n">
         <v>1</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -3971,9 +3920,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4119,9 +4065,6 @@
       <c r="O23" t="n">
         <v>83</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>1.124874332563269</v>
       </c>
@@ -4267,9 +4210,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4415,9 +4355,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4563,9 +4500,6 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -4711,9 +4645,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4859,9 +4790,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5007,9 +4935,6 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -5155,9 +5080,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5303,9 +5225,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5451,9 +5370,6 @@
       <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -5599,9 +5515,6 @@
       <c r="O33" t="n">
         <v>166</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>2.249748665126538</v>
       </c>
@@ -5747,9 +5660,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -5895,9 +5805,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6043,9 +5950,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -6187,9 +6091,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6335,9 +6236,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -6483,9 +6381,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6631,9 +6526,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -6779,9 +6671,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -6927,9 +6816,6 @@
       <c r="O42" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -7075,9 +6961,6 @@
       <c r="O43" t="n">
         <v>16</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.2168432448314735</v>
       </c>
@@ -7223,9 +7106,6 @@
       <c r="O44" t="n">
         <v>7</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -7371,9 +7251,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7519,9 +7396,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -7667,9 +7541,6 @@
       <c r="O47" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -7815,9 +7686,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -7963,9 +7831,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8111,9 +7976,6 @@
       <c r="O50" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -8259,9 +8121,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -8407,9 +8266,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -8555,9 +8411,6 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -8703,9 +8556,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -8851,9 +8701,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -8999,9 +8846,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -9147,9 +8991,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9295,9 +9136,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -9443,9 +9281,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9591,9 +9426,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -9739,9 +9571,6 @@
       <c r="O61" t="n">
         <v>19</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.2575013532373748</v>
       </c>
@@ -9887,9 +9716,6 @@
       <c r="O62" t="n">
         <v>40</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.5421081120786837</v>
       </c>
@@ -10035,9 +9861,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10183,9 +10006,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10345,9 +10165,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10493,9 +10310,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -10641,9 +10455,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10789,9 +10600,6 @@
       <c r="O68" t="n">
         <v>4</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -10937,9 +10745,6 @@
       <c r="O69" t="n">
         <v>7</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -11085,9 +10890,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11233,9 +11035,6 @@
       <c r="O71" t="n">
         <v>3</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -11381,9 +11180,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11529,9 +11325,6 @@
       <c r="O73" t="n">
         <v>13</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.1761851364255722</v>
       </c>
@@ -11677,9 +11470,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -11912,7 +11702,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -12142,7 +11932,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -12372,7 +12162,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -12515,9 +12305,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12663,9 +12450,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12811,9 +12595,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -12959,9 +12740,6 @@
       <c r="O81" t="n">
         <v>4</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -13107,9 +12885,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13255,9 +13030,6 @@
       <c r="O83" t="n">
         <v>194</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>2.629224343581616</v>
       </c>
@@ -13403,9 +13175,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -13551,9 +13320,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13699,9 +13465,6 @@
       <c r="O86" t="n">
         <v>55</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.7453986541081902</v>
       </c>
@@ -13847,9 +13610,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -13995,9 +13755,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14143,9 +13900,6 @@
       <c r="O89" t="n">
         <v>3</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -14291,9 +14045,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -14439,9 +14190,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14587,9 +14335,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -14735,9 +14480,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14883,9 +14625,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15031,9 +14770,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15179,9 +14915,6 @@
       <c r="O96" t="n">
         <v>148</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>2.00580001469113</v>
       </c>
@@ -15327,9 +15060,6 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -15475,9 +15205,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15623,9 +15350,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15767,9 +15491,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -15915,9 +15636,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -16063,9 +15781,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -16211,9 +15926,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16359,9 +16071,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -16507,9 +16216,6 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -16655,9 +16361,6 @@
       <c r="O106" t="n">
         <v>13</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.1761851364255722</v>
       </c>
@@ -16803,9 +16506,6 @@
       <c r="O107" t="n">
         <v>4</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -16951,9 +16651,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -17099,9 +16796,6 @@
       <c r="O109" t="n">
         <v>2</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -17247,9 +16941,6 @@
       <c r="O110" t="n">
         <v>2</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -17395,9 +17086,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17543,9 +17231,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -17691,9 +17376,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -17839,9 +17521,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -17987,9 +17666,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18135,9 +17811,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -18283,9 +17956,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18431,9 +18101,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -18579,9 +18246,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -18727,9 +18391,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -18875,9 +18536,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -19023,9 +18681,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -19171,9 +18826,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19319,9 +18971,6 @@
       <c r="O124" t="n">
         <v>40</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.5421081120786837</v>
       </c>
@@ -19467,9 +19116,6 @@
       <c r="O125" t="n">
         <v>20</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.2710540560393419</v>
       </c>
@@ -19615,9 +19261,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -19763,9 +19406,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -19925,9 +19565,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -20073,9 +19710,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -20221,9 +19855,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -20369,9 +20000,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -20517,9 +20145,6 @@
       <c r="O132" t="n">
         <v>8</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.1084216224157367</v>
       </c>
@@ -20665,9 +20290,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -20813,9 +20435,6 @@
       <c r="O134" t="n">
         <v>3</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -20961,9 +20580,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -21109,9 +20725,6 @@
       <c r="O136" t="n">
         <v>14</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.1897378392275393</v>
       </c>
@@ -21257,9 +20870,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -21492,7 +21102,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -21722,7 +21332,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -21952,7 +21562,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -22095,9 +21705,6 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -22243,9 +21850,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -22391,9 +21995,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -22539,9 +22140,6 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -22687,9 +22285,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -22835,9 +22430,6 @@
       <c r="O146" t="n">
         <v>224</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>3.035805427640629</v>
       </c>
@@ -22983,9 +22575,6 @@
       <c r="O147" t="n">
         <v>1</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -23131,9 +22720,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -23279,9 +22865,6 @@
       <c r="O149" t="n">
         <v>80</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>1.084216224157367</v>
       </c>
@@ -23427,9 +23010,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -23575,9 +23155,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -23723,9 +23300,6 @@
       <c r="O152" t="n">
         <v>5</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -23871,9 +23445,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -24019,9 +23590,6 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -24167,9 +23735,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -24315,9 +23880,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -24463,9 +24025,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -24611,9 +24170,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -24759,9 +24315,6 @@
       <c r="O159" t="n">
         <v>156</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>2.114221637106867</v>
       </c>
@@ -24907,9 +24460,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -25055,9 +24605,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -25203,9 +24750,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -25347,9 +24891,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -25495,9 +25036,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -25643,9 +25181,6 @@
       <c r="O165" t="n">
         <v>1</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -25791,9 +25326,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -25939,9 +25471,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -26087,9 +25616,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -26235,9 +25761,6 @@
       <c r="O169" t="n">
         <v>10</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.1355270280196709</v>
       </c>
@@ -26383,9 +25906,6 @@
       <c r="O170" t="n">
         <v>10</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.1355270280196709</v>
       </c>
@@ -26531,9 +26051,6 @@
       <c r="O171" t="n">
         <v>2</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -26679,9 +26196,6 @@
       <c r="O172" t="n">
         <v>2</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -26827,9 +26341,6 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -26975,9 +26486,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -27123,9 +26631,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -27271,9 +26776,6 @@
       <c r="O176" t="n">
         <v>3</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -27419,9 +26921,6 @@
       <c r="O177" t="n">
         <v>1</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -27567,9 +27066,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -27715,9 +27211,6 @@
       <c r="O179" t="n">
         <v>3</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -27863,9 +27356,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -28011,9 +27501,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -28159,9 +27646,6 @@
       <c r="O182" t="n">
         <v>4</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -28307,9 +27791,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -28455,9 +27936,6 @@
       <c r="O184" t="n">
         <v>1</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -28603,9 +28081,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -28751,9 +28226,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -28899,9 +28371,6 @@
       <c r="O187" t="n">
         <v>7</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -29047,9 +28516,6 @@
       <c r="O188" t="n">
         <v>33</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.4472391924649141</v>
       </c>
@@ -29195,9 +28661,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -29343,9 +28806,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -29592,7 +29052,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -29739,9 +29199,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -29887,9 +29344,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -30035,9 +29489,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -30183,9 +29634,6 @@
       <c r="O195" t="n">
         <v>4</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -30331,9 +29779,6 @@
       <c r="O196" t="n">
         <v>4</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -30479,9 +29924,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -30627,9 +30069,6 @@
       <c r="O198" t="n">
         <v>2</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -30775,9 +30214,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -30923,9 +30359,6 @@
       <c r="O200" t="n">
         <v>12</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.1626324336236051</v>
       </c>
@@ -31071,9 +30504,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -31306,7 +30736,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -31536,7 +30966,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -31766,7 +31196,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -31909,9 +31339,6 @@
       <c r="O205" t="n">
         <v>6</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.08131621681180255</v>
       </c>
@@ -32057,9 +31484,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -32205,9 +31629,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -32353,9 +31774,6 @@
       <c r="O208" t="n">
         <v>7</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -32501,9 +31919,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -32649,9 +32064,6 @@
       <c r="O210" t="n">
         <v>222</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>3.008700022036694</v>
       </c>
@@ -32797,9 +32209,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -32945,9 +32354,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -33093,9 +32499,6 @@
       <c r="O213" t="n">
         <v>63</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.8538202765239269</v>
       </c>
@@ -33241,9 +32644,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -33389,9 +32789,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -33537,9 +32934,6 @@
       <c r="O216" t="n">
         <v>2</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -33685,9 +33079,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -33833,9 +33224,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -33981,9 +33369,6 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
@@ -34129,9 +33514,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -34277,9 +33659,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -34425,9 +33804,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -34573,9 +33949,6 @@
       <c r="O223" t="n">
         <v>108</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>1.463691902612446</v>
       </c>
@@ -34721,9 +34094,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -34869,9 +34239,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -35017,9 +34384,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -35161,9 +34525,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -35309,9 +34670,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -35457,9 +34815,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -35605,9 +34960,6 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -35753,9 +35105,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -35901,9 +35250,6 @@
       <c r="O232" t="n">
         <v>2</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -36049,9 +35395,6 @@
       <c r="O233" t="n">
         <v>12</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.1626324336236051</v>
       </c>
@@ -36197,9 +35540,6 @@
       <c r="O234" t="n">
         <v>19</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.2575013532373748</v>
       </c>
@@ -36345,9 +35685,6 @@
       <c r="O235" t="n">
         <v>1</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -36493,9 +35830,6 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -36641,9 +35975,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -36789,9 +36120,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -36937,9 +36265,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -37085,9 +36410,6 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -37233,9 +36555,6 @@
       <c r="O241" t="n">
         <v>1</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -37381,9 +36700,6 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -37529,9 +36845,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -37677,9 +36990,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
@@ -37825,9 +37135,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -37973,9 +37280,6 @@
       <c r="O246" t="n">
         <v>2</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -38121,9 +37425,6 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
@@ -38269,9 +37570,6 @@
       <c r="O248" t="n">
         <v>2</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -38417,9 +37715,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -38565,9 +37860,6 @@
       <c r="O250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
@@ -38713,9 +38005,6 @@
       <c r="O251" t="n">
         <v>9</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.1219743252177038</v>
       </c>
@@ -38861,9 +38150,6 @@
       <c r="O252" t="n">
         <v>30</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.4065810840590128</v>
       </c>
@@ -39009,9 +38295,6 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
@@ -39157,9 +38440,6 @@
       <c r="O254" t="n">
         <v>1</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -39406,7 +38686,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -39553,9 +38833,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -39701,9 +38978,6 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
@@ -39849,9 +39123,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -39997,9 +39268,6 @@
       <c r="O259" t="n">
         <v>7</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -40145,9 +39413,6 @@
       <c r="O260" t="n">
         <v>5</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -40293,9 +39558,6 @@
       <c r="O261" t="n">
         <v>1</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -40441,9 +39703,6 @@
       <c r="O262" t="n">
         <v>7</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -40589,9 +39848,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -40737,9 +39993,6 @@
       <c r="O264" t="n">
         <v>15</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.2032905420295064</v>
       </c>
@@ -40885,9 +40138,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -41120,7 +40370,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -41350,7 +40600,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -41580,7 +40830,7 @@
       </c>
       <c r="AM268" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN268" t="b">
@@ -41723,9 +40973,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -41871,9 +41118,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -42019,9 +41263,6 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -42167,9 +41408,6 @@
       <c r="O272" t="n">
         <v>4</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -42315,9 +41553,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -42463,9 +41698,6 @@
       <c r="O274" t="n">
         <v>251</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>3.40172840329374</v>
       </c>
@@ -42611,9 +41843,6 @@
       <c r="O275" t="n">
         <v>1</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -42759,9 +41988,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -42907,9 +42133,6 @@
       <c r="O277" t="n">
         <v>77</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>1.043558115751466</v>
       </c>
@@ -43055,9 +42278,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -43203,9 +42423,6 @@
       <c r="O279" t="n">
         <v>1</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -43351,9 +42568,6 @@
       <c r="O280" t="n">
         <v>3</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -43499,9 +42713,6 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
@@ -43647,9 +42858,6 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0</v>
       </c>
@@ -43795,9 +43003,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -43943,9 +43148,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -44091,9 +43293,6 @@
       <c r="O285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -44239,9 +43438,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -44387,9 +43583,6 @@
       <c r="O287" t="n">
         <v>137</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>1.856720283869492</v>
       </c>
@@ -44535,9 +43728,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -44683,9 +43873,6 @@
       <c r="O289" t="n">
         <v>2</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -44831,9 +44018,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -44975,9 +44159,6 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -45123,9 +44304,6 @@
       <c r="O292" t="n">
         <v>3</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -45271,9 +44449,6 @@
       <c r="O293" t="n">
         <v>1</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -45419,9 +44594,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -45567,9 +44739,6 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -45715,9 +44884,6 @@
       <c r="O296" t="n">
         <v>1</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -45863,9 +45029,6 @@
       <c r="O297" t="n">
         <v>6</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.08131621681180255</v>
       </c>
@@ -46011,9 +45174,6 @@
       <c r="O298" t="n">
         <v>28</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.3794756784550786</v>
       </c>
@@ -46159,9 +45319,6 @@
       <c r="O299" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0</v>
       </c>
@@ -46307,9 +45464,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -46455,9 +45609,6 @@
       <c r="O301" t="n">
         <v>1</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -46603,9 +45754,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -46751,9 +45899,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -46899,9 +46044,6 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
@@ -47047,9 +46189,6 @@
       <c r="O305" t="n">
         <v>1</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -47195,9 +46334,6 @@
       <c r="O306" t="n">
         <v>0</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0</v>
       </c>
@@ -47343,9 +46479,6 @@
       <c r="O307" t="n">
         <v>1</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -47491,9 +46624,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -47639,9 +46769,6 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
@@ -47787,9 +46914,6 @@
       <c r="O310" t="n">
         <v>1</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -47935,9 +47059,6 @@
       <c r="O311" t="n">
         <v>0</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0</v>
       </c>
@@ -48083,9 +47204,6 @@
       <c r="O312" t="n">
         <v>3</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -48231,9 +47349,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -48379,9 +47494,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -48527,9 +47639,6 @@
       <c r="O315" t="n">
         <v>10</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0.1355270280196709</v>
       </c>
@@ -48675,9 +47784,6 @@
       <c r="O316" t="n">
         <v>28</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0.3794756784550786</v>
       </c>
@@ -48823,9 +47929,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -48971,9 +48074,6 @@
       <c r="O318" t="n">
         <v>2</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -49220,7 +48320,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -49367,9 +48467,6 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -49515,9 +48612,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -49663,9 +48757,6 @@
       <c r="O322" t="n">
         <v>0</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0</v>
       </c>
@@ -49811,9 +48902,6 @@
       <c r="O323" t="n">
         <v>60</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.8131621681180257</v>
       </c>
@@ -49959,9 +49047,6 @@
       <c r="O324" t="n">
         <v>5</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -50107,9 +49192,6 @@
       <c r="O325" t="n">
         <v>0</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0</v>
       </c>
@@ -50255,9 +49337,6 @@
       <c r="O326" t="n">
         <v>5</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -50403,9 +49482,6 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
@@ -50551,9 +49627,6 @@
       <c r="O328" t="n">
         <v>21</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0.284606758841309</v>
       </c>
@@ -50699,9 +49772,6 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -50934,7 +50004,7 @@
       </c>
       <c r="AM330" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN330" t="b">
@@ -51164,7 +50234,7 @@
       </c>
       <c r="AM331" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN331" t="b">
@@ -51394,7 +50464,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -51537,9 +50607,6 @@
       <c r="O333" t="n">
         <v>1</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -51685,9 +50752,6 @@
       <c r="O334" t="n">
         <v>0</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0</v>
       </c>
@@ -51833,9 +50897,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -51981,9 +51042,6 @@
       <c r="O336" t="n">
         <v>3</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -52129,9 +51187,6 @@
       <c r="O337" t="n">
         <v>0</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0</v>
       </c>
@@ -52277,9 +51332,6 @@
       <c r="O338" t="n">
         <v>262</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>3.550808134115378</v>
       </c>
@@ -52425,9 +51477,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -52573,9 +51622,6 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0</v>
       </c>
@@ -52721,9 +51767,6 @@
       <c r="O341" t="n">
         <v>81</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>1.097768926959335</v>
       </c>
@@ -52869,9 +51912,6 @@
       <c r="O342" t="n">
         <v>0</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0</v>
       </c>
@@ -53017,9 +52057,6 @@
       <c r="O343" t="n">
         <v>2</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -53165,9 +52202,6 @@
       <c r="O344" t="n">
         <v>4</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -53313,9 +52347,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -53461,9 +52492,6 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
@@ -53609,9 +52637,6 @@
       <c r="O347" t="n">
         <v>0</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0</v>
       </c>
@@ -53757,9 +52782,6 @@
       <c r="O348" t="n">
         <v>0</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0</v>
       </c>
@@ -53905,9 +52927,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -54053,9 +53072,6 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0</v>
       </c>
@@ -54201,9 +53217,6 @@
       <c r="O351" t="n">
         <v>147</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>1.992247311889163</v>
       </c>
@@ -54349,9 +53362,6 @@
       <c r="O352" t="n">
         <v>1</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -54497,9 +53507,6 @@
       <c r="O353" t="n">
         <v>3</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -54645,9 +53652,6 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0</v>
       </c>
@@ -54789,9 +53793,6 @@
       <c r="O355" t="n">
         <v>0</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0</v>
       </c>
@@ -54937,9 +53938,6 @@
       <c r="O356" t="n">
         <v>5</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0.06776351400983546</v>
       </c>
@@ -55085,9 +54083,6 @@
       <c r="O357" t="n">
         <v>0</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0</v>
       </c>
@@ -55233,9 +54228,6 @@
       <c r="O358" t="n">
         <v>0</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0</v>
       </c>
@@ -55381,9 +54373,6 @@
       <c r="O359" t="n">
         <v>0</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0</v>
       </c>
@@ -55529,9 +54518,6 @@
       <c r="O360" t="n">
         <v>2</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -55677,9 +54663,6 @@
       <c r="O361" t="n">
         <v>7</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0.09486891961376966</v>
       </c>
@@ -55825,9 +54808,6 @@
       <c r="O362" t="n">
         <v>19</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.2575013532373748</v>
       </c>
@@ -55973,9 +54953,6 @@
       <c r="O363" t="n">
         <v>3</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -56121,9 +55098,6 @@
       <c r="O364" t="n">
         <v>0</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0</v>
       </c>
@@ -56269,9 +55243,6 @@
       <c r="O365" t="n">
         <v>2</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -56417,9 +55388,6 @@
       <c r="O366" t="n">
         <v>0</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0</v>
       </c>
@@ -56565,9 +55533,6 @@
       <c r="O367" t="n">
         <v>2</v>
       </c>
-      <c r="Q367" t="n">
-        <v>0</v>
-      </c>
       <c r="R367" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -56713,9 +55678,6 @@
       <c r="O368" t="n">
         <v>1</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -56861,9 +55823,6 @@
       <c r="O369" t="n">
         <v>3</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -57009,9 +55968,6 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0</v>
       </c>
@@ -57157,9 +56113,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -57305,9 +56258,6 @@
       <c r="O372" t="n">
         <v>0</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0</v>
       </c>
@@ -57453,9 +56403,6 @@
       <c r="O373" t="n">
         <v>0</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0</v>
       </c>
@@ -57601,9 +56548,6 @@
       <c r="O374" t="n">
         <v>4</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0.05421081120786837</v>
       </c>
@@ -57749,9 +56693,6 @@
       <c r="O375" t="n">
         <v>0</v>
       </c>
-      <c r="Q375" t="n">
-        <v>0</v>
-      </c>
       <c r="R375" t="n">
         <v>0</v>
       </c>
@@ -57897,9 +56838,6 @@
       <c r="O376" t="n">
         <v>2</v>
       </c>
-      <c r="Q376" t="n">
-        <v>0</v>
-      </c>
       <c r="R376" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -58045,9 +56983,6 @@
       <c r="O377" t="n">
         <v>0</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0</v>
       </c>
@@ -58193,9 +57128,6 @@
       <c r="O378" t="n">
         <v>0</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>0</v>
       </c>
@@ -58341,9 +57273,6 @@
       <c r="O379" t="n">
         <v>10</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0.1355270280196709</v>
       </c>
@@ -58489,9 +57418,6 @@
       <c r="O380" t="n">
         <v>30</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0.4065810840590128</v>
       </c>
@@ -58637,9 +57563,6 @@
       <c r="O381" t="n">
         <v>0</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0</v>
       </c>
@@ -58785,9 +57708,6 @@
       <c r="O382" t="n">
         <v>1</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -59034,7 +57954,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN383" t="b">

--- a/countries/hk/2026-2029.xlsx
+++ b/countries/hk/2026-2029.xlsx
@@ -38145,13 +38145,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="O252" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R252" t="n">
-        <v>0.4065810840590128</v>
+        <v>0.4878973008708154</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -46909,13 +46909,13 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O310" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R310" t="n">
-        <v>0.01355270280196709</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -47779,13 +47779,13 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O316" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R316" t="n">
-        <v>0.3794756784550786</v>
+        <v>0.4065810840590128</v>
       </c>
       <c r="S316" t="inlineStr">
         <is>
@@ -53502,13 +53502,13 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O353" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R353" t="n">
-        <v>0.04065810840590128</v>
+        <v>0.05421081120786837</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
@@ -57413,13 +57413,13 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O380" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R380" t="n">
-        <v>0.4065810840590128</v>
+        <v>0.4472391924649141</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
@@ -58024,6 +58024,9640 @@
         </is>
       </c>
       <c r="BC383" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Plague</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>鼠疫</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N384" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" t="n">
+        <v>0</v>
+      </c>
+      <c r="R384" t="n">
+        <v>0</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO384" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP384" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR384" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr"/>
+      <c r="AT384" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU384" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV384" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW384" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX384" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY384" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA384" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB384" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC384" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N385" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" t="n">
+        <v>0</v>
+      </c>
+      <c r="R385" t="n">
+        <v>0</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO385" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP385" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR385" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS385" t="inlineStr"/>
+      <c r="AT385" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU385" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV385" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW385" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX385" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY385" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA385" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB385" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC385" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>SARS</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>传染性非典型肺炎</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N386" t="n">
+        <v>0</v>
+      </c>
+      <c r="O386" t="n">
+        <v>0</v>
+      </c>
+      <c r="R386" t="n">
+        <v>0</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO386" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP386" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR386" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS386" t="inlineStr"/>
+      <c r="AT386" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU386" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV386" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW386" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX386" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY386" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA386" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB386" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC386" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N387" t="n">
+        <v>249</v>
+      </c>
+      <c r="O387" t="n">
+        <v>249</v>
+      </c>
+      <c r="R387" t="n">
+        <v>3.374622997689806</v>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO387" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP387" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR387" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS387" t="inlineStr"/>
+      <c r="AT387" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU387" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV387" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW387" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX387" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY387" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA387" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB387" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC387" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N388" t="n">
+        <v>2</v>
+      </c>
+      <c r="O388" t="n">
+        <v>2</v>
+      </c>
+      <c r="R388" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO388" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP388" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR388" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS388" t="inlineStr"/>
+      <c r="AT388" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU388" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV388" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW388" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX388" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY388" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA388" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB388" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC388" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Hepatitis B</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N389" t="n">
+        <v>0</v>
+      </c>
+      <c r="O389" t="n">
+        <v>0</v>
+      </c>
+      <c r="R389" t="n">
+        <v>0</v>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO389" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP389" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR389" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS389" t="inlineStr"/>
+      <c r="AT389" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU389" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV389" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW389" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX389" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY389" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA389" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB389" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC389" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>D009</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Hepatitis C</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N390" t="n">
+        <v>2</v>
+      </c>
+      <c r="O390" t="n">
+        <v>2</v>
+      </c>
+      <c r="R390" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO390" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP390" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR390" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS390" t="inlineStr"/>
+      <c r="AT390" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU390" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV390" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW390" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX390" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY390" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA390" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB390" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC390" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
+      <c r="R391" t="n">
+        <v>0</v>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO391" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP391" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR391" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS391" t="inlineStr"/>
+      <c r="AT391" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU391" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV391" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW391" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX391" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY391" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA391" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB391" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC391" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N392" t="n">
+        <v>17</v>
+      </c>
+      <c r="O392" t="n">
+        <v>17</v>
+      </c>
+      <c r="R392" t="n">
+        <v>0.2303959476334406</v>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO392" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP392" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR392" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS392" t="inlineStr"/>
+      <c r="AT392" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU392" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV392" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW392" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX392" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY392" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA392" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB392" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC392" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>D013</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Poliomyelitis</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>脊髓灰质炎</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N393" t="n">
+        <v>0</v>
+      </c>
+      <c r="O393" t="n">
+        <v>0</v>
+      </c>
+      <c r="R393" t="n">
+        <v>0</v>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO393" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP393" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR393" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS393" t="inlineStr"/>
+      <c r="AT393" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU393" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV393" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW393" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX393" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY393" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA393" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB393" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC393" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N394" t="n">
+        <v>0</v>
+      </c>
+      <c r="O394" t="n">
+        <v>0</v>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_H5</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_H5</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>SRC_HK_CHP</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>Influenza A - Influenza A (H5)</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB394" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>country:HK:national</t>
+        </is>
+      </c>
+      <c r="AD394" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE394" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF394" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG394" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH394" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI394" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ394" t="inlineStr">
+        <is>
+          <t>HK_CHP_H5_current</t>
+        </is>
+      </c>
+      <c r="AK394" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP H5 novel influenza A category.</t>
+        </is>
+      </c>
+      <c r="AM394" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN394" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO394" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP394" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ394" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS394" t="inlineStr"/>
+      <c r="AT394" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU394" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV394" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW394" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX394" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY394" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA394" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB394" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC394" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N395" t="n">
+        <v>0</v>
+      </c>
+      <c r="O395" t="n">
+        <v>0</v>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_H7</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_H7</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>SRC_HK_CHP</t>
+        </is>
+      </c>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>Influenza A - Influenza A (H7)</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB395" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC395" t="inlineStr">
+        <is>
+          <t>country:HK:national</t>
+        </is>
+      </c>
+      <c r="AD395" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE395" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF395" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG395" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH395" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI395" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ395" t="inlineStr">
+        <is>
+          <t>HK_CHP_H7_current</t>
+        </is>
+      </c>
+      <c r="AK395" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP H7 novel influenza A category.</t>
+        </is>
+      </c>
+      <c r="AM395" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN395" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO395" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP395" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ395" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS395" t="inlineStr"/>
+      <c r="AT395" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU395" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV395" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW395" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX395" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY395" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA395" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB395" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC395" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N396" t="n">
+        <v>0</v>
+      </c>
+      <c r="O396" t="n">
+        <v>0</v>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_OTHERS</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_OTHERS</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>SRC_HK_CHP</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>Novel influenza A infection - Others</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB396" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC396" t="inlineStr">
+        <is>
+          <t>country:HK:national</t>
+        </is>
+      </c>
+      <c r="AD396" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE396" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF396" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG396" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH396" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI396" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ396" t="inlineStr">
+        <is>
+          <t>HK_CHP_other_current</t>
+        </is>
+      </c>
+      <c r="AK396" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP residual novel influenza A category.</t>
+        </is>
+      </c>
+      <c r="AM396" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN396" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO396" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP396" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ396" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS396" t="inlineStr"/>
+      <c r="AT396" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU396" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV396" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW396" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX396" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY396" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA396" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB396" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC396" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N397" t="n">
+        <v>0</v>
+      </c>
+      <c r="O397" t="n">
+        <v>0</v>
+      </c>
+      <c r="R397" t="n">
+        <v>0</v>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO397" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP397" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR397" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS397" t="inlineStr"/>
+      <c r="AT397" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU397" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV397" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW397" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX397" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY397" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA397" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB397" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC397" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Rabies</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>狂犬病</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N398" t="n">
+        <v>0</v>
+      </c>
+      <c r="O398" t="n">
+        <v>0</v>
+      </c>
+      <c r="R398" t="n">
+        <v>0</v>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO398" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP398" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR398" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS398" t="inlineStr"/>
+      <c r="AT398" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU398" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV398" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW398" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX398" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY398" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA398" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB398" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC398" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N399" t="n">
+        <v>0</v>
+      </c>
+      <c r="O399" t="n">
+        <v>0</v>
+      </c>
+      <c r="R399" t="n">
+        <v>0</v>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO399" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP399" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR399" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS399" t="inlineStr"/>
+      <c r="AT399" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU399" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV399" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW399" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX399" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY399" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA399" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB399" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC399" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>D021</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Dengue</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>登革热</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N400" t="n">
+        <v>3</v>
+      </c>
+      <c r="O400" t="n">
+        <v>3</v>
+      </c>
+      <c r="R400" t="n">
+        <v>0.04065810840590128</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO400" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP400" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR400" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS400" t="inlineStr"/>
+      <c r="AT400" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU400" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV400" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW400" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX400" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY400" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA400" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB400" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC400" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>D023</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Anthrax</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>炭疽</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N401" t="n">
+        <v>0</v>
+      </c>
+      <c r="O401" t="n">
+        <v>0</v>
+      </c>
+      <c r="R401" t="n">
+        <v>0</v>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO401" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP401" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR401" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS401" t="inlineStr"/>
+      <c r="AT401" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU401" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV401" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW401" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX401" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY401" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA401" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB401" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC401" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N402" t="n">
+        <v>279</v>
+      </c>
+      <c r="O402" t="n">
+        <v>279</v>
+      </c>
+      <c r="R402" t="n">
+        <v>3.78120408174882</v>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO402" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP402" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR402" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS402" t="inlineStr"/>
+      <c r="AT402" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU402" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV402" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW402" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX402" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY402" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA402" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB402" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC402" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N403" t="n">
+        <v>1</v>
+      </c>
+      <c r="O403" t="n">
+        <v>1</v>
+      </c>
+      <c r="R403" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO403" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP403" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR403" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS403" t="inlineStr"/>
+      <c r="AT403" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU403" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV403" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW403" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX403" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY403" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA403" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB403" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC403" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N404" t="n">
+        <v>0</v>
+      </c>
+      <c r="O404" t="n">
+        <v>0</v>
+      </c>
+      <c r="R404" t="n">
+        <v>0</v>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO404" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP404" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR404" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS404" t="inlineStr"/>
+      <c r="AT404" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU404" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV404" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW404" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX404" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY404" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA404" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB404" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC404" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>D031</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Scarlet fever</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>猩红热</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N405" t="n">
+        <v>62</v>
+      </c>
+      <c r="O405" t="n">
+        <v>62</v>
+      </c>
+      <c r="R405" t="n">
+        <v>0.8402675737219598</v>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO405" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP405" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR405" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS405" t="inlineStr"/>
+      <c r="AT405" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU405" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV405" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW405" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX405" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY405" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA405" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB405" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC405" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>D035</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Leptospirosis</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>钩端螺旋体病</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N406" t="n">
+        <v>0</v>
+      </c>
+      <c r="O406" t="n">
+        <v>0</v>
+      </c>
+      <c r="R406" t="n">
+        <v>0</v>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO406" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP406" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR406" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS406" t="inlineStr"/>
+      <c r="AT406" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU406" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV406" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW406" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX406" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY406" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA406" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB406" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC406" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N407" t="n">
+        <v>2</v>
+      </c>
+      <c r="O407" t="n">
+        <v>2</v>
+      </c>
+      <c r="R407" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO407" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP407" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR407" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS407" t="inlineStr"/>
+      <c r="AT407" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU407" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV407" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW407" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX407" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY407" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA407" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB407" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC407" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>0</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
+      <c r="R408" t="n">
+        <v>0</v>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO408" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP408" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR408" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS408" t="inlineStr"/>
+      <c r="AT408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU408" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV408" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW408" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX408" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY408" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA408" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB408" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC408" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>0</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0</v>
+      </c>
+      <c r="R409" t="n">
+        <v>0</v>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO409" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP409" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR409" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS409" t="inlineStr"/>
+      <c r="AT409" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU409" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV409" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW409" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX409" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY409" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA409" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB409" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC409" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>D042</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Leprosy</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>麻风病</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N410" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" t="n">
+        <v>0</v>
+      </c>
+      <c r="R410" t="n">
+        <v>0</v>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO410" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP410" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR410" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS410" t="inlineStr"/>
+      <c r="AT410" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU410" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV410" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW410" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX410" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY410" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA410" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB410" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC410" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>D043</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Typhus</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>流行性和地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N411" t="n">
+        <v>0</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
+      <c r="R411" t="n">
+        <v>0</v>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO411" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP411" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR411" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS411" t="inlineStr"/>
+      <c r="AT411" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU411" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV411" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW411" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX411" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY411" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA411" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB411" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC411" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>D049</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>MERS</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>中东呼吸综合征</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>0</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0</v>
+      </c>
+      <c r="R412" t="n">
+        <v>0</v>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO412" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP412" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR412" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS412" t="inlineStr"/>
+      <c r="AT412" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU412" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV412" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW412" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX412" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY412" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA412" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB412" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC412" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>D051</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Zika virus disease</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>寨卡病毒病</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N413" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0</v>
+      </c>
+      <c r="R413" t="n">
+        <v>0</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO413" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP413" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR413" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS413" t="inlineStr"/>
+      <c r="AT413" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU413" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV413" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW413" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX413" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY413" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA413" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB413" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC413" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>D052</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Chikungunya</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>基孔肯雅热</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N414" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+      <c r="R414" t="n">
+        <v>0</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO414" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP414" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR414" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS414" t="inlineStr"/>
+      <c r="AT414" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU414" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV414" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW414" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX414" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY414" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA414" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB414" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC414" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Varicella</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>水痘</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N415" t="n">
+        <v>136</v>
+      </c>
+      <c r="O415" t="n">
+        <v>136</v>
+      </c>
+      <c r="R415" t="n">
+        <v>1.843167581067525</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO415" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP415" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR415" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS415" t="inlineStr"/>
+      <c r="AT415" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU415" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV415" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW415" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX415" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY415" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA415" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB415" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC415" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>D056</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Streptococcus suis</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>人感染猪链球菌病</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N416" t="n">
+        <v>0</v>
+      </c>
+      <c r="O416" t="n">
+        <v>0</v>
+      </c>
+      <c r="R416" t="n">
+        <v>0</v>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO416" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP416" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR416" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS416" t="inlineStr"/>
+      <c r="AT416" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU416" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV416" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW416" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX416" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY416" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA416" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB416" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC416" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>D058</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Scrub Typhus</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>恙虫病</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N417" t="n">
+        <v>1</v>
+      </c>
+      <c r="O417" t="n">
+        <v>1</v>
+      </c>
+      <c r="R417" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO417" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP417" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR417" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS417" t="inlineStr"/>
+      <c r="AT417" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU417" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV417" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW417" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX417" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY417" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA417" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB417" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC417" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N418" t="n">
+        <v>0</v>
+      </c>
+      <c r="O418" t="n">
+        <v>0</v>
+      </c>
+      <c r="R418" t="n">
+        <v>0</v>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO418" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP418" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR418" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS418" t="inlineStr"/>
+      <c r="AT418" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU418" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV418" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW418" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX418" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY418" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA418" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB418" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC418" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N419" t="n">
+        <v>0</v>
+      </c>
+      <c r="O419" t="n">
+        <v>0</v>
+      </c>
+      <c r="R419" t="n">
+        <v>0</v>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO419" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP419" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR419" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS419" t="inlineStr"/>
+      <c r="AT419" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU419" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV419" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW419" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX419" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY419" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA419" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB419" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC419" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>D065</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Monkeypox</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>猴痘</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N420" t="n">
+        <v>1</v>
+      </c>
+      <c r="O420" t="n">
+        <v>1</v>
+      </c>
+      <c r="R420" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO420" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP420" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR420" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS420" t="inlineStr"/>
+      <c r="AT420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU420" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV420" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW420" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX420" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY420" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA420" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB420" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC420" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>D091</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Botulism</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>肉毒杆菌中毒</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N421" t="n">
+        <v>0</v>
+      </c>
+      <c r="O421" t="n">
+        <v>0</v>
+      </c>
+      <c r="R421" t="n">
+        <v>0</v>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO421" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP421" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR421" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS421" t="inlineStr"/>
+      <c r="AT421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU421" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV421" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW421" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX421" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY421" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA421" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB421" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC421" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N422" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" t="n">
+        <v>0</v>
+      </c>
+      <c r="R422" t="n">
+        <v>0</v>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO422" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP422" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR422" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS422" t="inlineStr"/>
+      <c r="AT422" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU422" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV422" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW422" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX422" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY422" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA422" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB422" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC422" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>D102</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Hantavirus infection</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>汉坦病毒感染</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N423" t="n">
+        <v>0</v>
+      </c>
+      <c r="O423" t="n">
+        <v>0</v>
+      </c>
+      <c r="R423" t="n">
+        <v>0</v>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO423" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP423" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR423" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS423" t="inlineStr"/>
+      <c r="AT423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU423" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV423" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW423" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX423" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY423" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA423" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB423" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC423" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N424" t="n">
+        <v>1</v>
+      </c>
+      <c r="O424" t="n">
+        <v>1</v>
+      </c>
+      <c r="R424" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO424" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP424" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR424" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS424" t="inlineStr"/>
+      <c r="AT424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU424" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV424" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW424" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX424" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY424" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA424" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB424" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC424" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N425" t="n">
+        <v>15</v>
+      </c>
+      <c r="O425" t="n">
+        <v>15</v>
+      </c>
+      <c r="R425" t="n">
+        <v>0.2032905420295064</v>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO425" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP425" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR425" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS425" t="inlineStr"/>
+      <c r="AT425" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU425" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV425" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW425" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX425" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY425" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA425" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB425" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC425" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N426" t="n">
+        <v>20</v>
+      </c>
+      <c r="O426" t="n">
+        <v>20</v>
+      </c>
+      <c r="R426" t="n">
+        <v>0.2710540560393419</v>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO426" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP426" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR426" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS426" t="inlineStr"/>
+      <c r="AT426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU426" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV426" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW426" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX426" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY426" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA426" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB426" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC426" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N427" t="n">
+        <v>1</v>
+      </c>
+      <c r="O427" t="n">
+        <v>1</v>
+      </c>
+      <c r="R427" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO427" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP427" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR427" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS427" t="inlineStr"/>
+      <c r="AT427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU427" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV427" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW427" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX427" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY427" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA427" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB427" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC427" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Meningococcal disease</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>脑膜炎球菌病</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N428" t="n">
+        <v>0</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0</v>
+      </c>
+      <c r="R428" t="n">
+        <v>0</v>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO428" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP428" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR428" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS428" t="inlineStr"/>
+      <c r="AT428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU428" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV428" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW428" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX428" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY428" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA428" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB428" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC428" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Psittacosis</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>鹦鹉热</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N429" t="n">
+        <v>0</v>
+      </c>
+      <c r="O429" t="n">
+        <v>0</v>
+      </c>
+      <c r="R429" t="n">
+        <v>0</v>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO429" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP429" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR429" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS429" t="inlineStr"/>
+      <c r="AT429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU429" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV429" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW429" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX429" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY429" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA429" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB429" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC429" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N430" t="n">
+        <v>0</v>
+      </c>
+      <c r="O430" t="n">
+        <v>0</v>
+      </c>
+      <c r="R430" t="n">
+        <v>0</v>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO430" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP430" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR430" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS430" t="inlineStr"/>
+      <c r="AT430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU430" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV430" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW430" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX430" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY430" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA430" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB430" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC430" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N431" t="n">
+        <v>0</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0</v>
+      </c>
+      <c r="R431" t="n">
+        <v>0</v>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO431" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP431" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR431" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS431" t="inlineStr"/>
+      <c r="AT431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU431" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV431" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW431" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX431" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY431" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA431" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB431" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC431" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Melioidosis</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>类鼻疽</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N432" t="n">
+        <v>0</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0</v>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO432" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP432" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR432" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS432" t="inlineStr"/>
+      <c r="AT432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU432" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV432" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW432" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX432" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY432" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA432" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB432" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC432" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>D118</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Spotted fever rickettsiosis</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>斑点热立克次体病</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N433" t="n">
+        <v>1</v>
+      </c>
+      <c r="O433" t="n">
+        <v>1</v>
+      </c>
+      <c r="R433" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO433" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP433" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR433" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS433" t="inlineStr"/>
+      <c r="AT433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU433" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV433" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW433" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX433" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY433" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA433" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB433" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC433" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Tetanus</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>破伤风</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N434" t="n">
+        <v>0</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
+      <c r="R434" t="n">
+        <v>0</v>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO434" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP434" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR434" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS434" t="inlineStr"/>
+      <c r="AT434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU434" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV434" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW434" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX434" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY434" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA434" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB434" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC434" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N435" t="n">
+        <v>2</v>
+      </c>
+      <c r="O435" t="n">
+        <v>2</v>
+      </c>
+      <c r="R435" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO435" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP435" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR435" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS435" t="inlineStr"/>
+      <c r="AT435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU435" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV435" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW435" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX435" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY435" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA435" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB435" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC435" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N436" t="n">
+        <v>0</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0</v>
+      </c>
+      <c r="R436" t="n">
+        <v>0</v>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO436" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP436" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR436" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS436" t="inlineStr"/>
+      <c r="AT436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU436" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV436" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW436" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX436" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY436" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA436" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB436" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC436" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N437" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+      <c r="R437" t="n">
+        <v>0</v>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO437" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP437" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR437" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS437" t="inlineStr"/>
+      <c r="AT437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU437" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV437" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW437" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX437" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY437" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA437" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB437" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC437" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>D144</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Creutzfeldt-Jakob disease</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>克雅氏病</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Prion</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N438" t="n">
+        <v>2</v>
+      </c>
+      <c r="O438" t="n">
+        <v>2</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO438" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP438" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR438" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS438" t="inlineStr"/>
+      <c r="AT438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU438" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV438" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW438" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX438" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY438" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA438" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB438" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC438" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>D145</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Relapsing fever</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>回归热</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N439" t="n">
+        <v>0</v>
+      </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+      <c r="R439" t="n">
+        <v>0</v>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO439" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP439" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR439" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS439" t="inlineStr"/>
+      <c r="AT439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU439" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV439" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW439" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX439" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY439" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA439" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB439" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC439" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>D165</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Amebiasis</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>阿米巴病</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N440" t="n">
+        <v>2</v>
+      </c>
+      <c r="O440" t="n">
+        <v>2</v>
+      </c>
+      <c r="R440" t="n">
+        <v>0.02710540560393419</v>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO440" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP440" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR440" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS440" t="inlineStr"/>
+      <c r="AT440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU440" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV440" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW440" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX440" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY440" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA440" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB440" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC440" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N441" t="n">
+        <v>0</v>
+      </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+      <c r="R441" t="n">
+        <v>0</v>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO441" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP441" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR441" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS441" t="inlineStr"/>
+      <c r="AT441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU441" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV441" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW441" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX441" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY441" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA441" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB441" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC441" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N442" t="n">
+        <v>0</v>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="R442" t="n">
+        <v>0</v>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO442" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP442" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR442" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS442" t="inlineStr"/>
+      <c r="AT442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU442" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV442" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW442" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX442" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY442" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA442" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB442" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC442" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>D196</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Foodborne disease outbreak</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>食源性疾病暴发</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N443" t="n">
+        <v>7</v>
+      </c>
+      <c r="O443" t="n">
+        <v>7</v>
+      </c>
+      <c r="R443" t="n">
+        <v>0.09486891961376966</v>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO443" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP443" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR443" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS443" t="inlineStr"/>
+      <c r="AT443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU443" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV443" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW443" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX443" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY443" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA443" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB443" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC443" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>D206</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Community-associated methicillin-resistant Staphylococcus aureus infection</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>社区相关耐甲氧西林金黄色葡萄球菌感染</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N444" t="n">
+        <v>30</v>
+      </c>
+      <c r="O444" t="n">
+        <v>30</v>
+      </c>
+      <c r="R444" t="n">
+        <v>0.4065810840590128</v>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO444" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP444" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR444" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS444" t="inlineStr"/>
+      <c r="AT444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU444" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV444" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW444" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX444" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY444" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA444" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB444" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC444" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>D207</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Enterovirus 71 infection</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>肠病毒71型感染</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N445" t="n">
+        <v>0</v>
+      </c>
+      <c r="O445" t="n">
+        <v>0</v>
+      </c>
+      <c r="R445" t="n">
+        <v>0</v>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO445" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP445" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR445" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS445" t="inlineStr"/>
+      <c r="AT445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU445" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV445" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW445" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX445" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY445" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA445" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB445" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC445" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N446" t="n">
+        <v>1</v>
+      </c>
+      <c r="O446" t="n">
+        <v>1</v>
+      </c>
+      <c r="R446" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO446" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP446" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ446" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS446" t="inlineStr">
+        <is>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT446" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU446" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV446" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW446" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX446" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY446" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA446" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB446" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC446" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N447" t="n">
+        <v>1</v>
+      </c>
+      <c r="O447" t="n">
+        <v>1</v>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>SRC_HK_CHP</t>
+        </is>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z447" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB447" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC447" t="inlineStr">
+        <is>
+          <t>country:HK:national</t>
+        </is>
+      </c>
+      <c r="AD447" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE447" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF447" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG447" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI447" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ447" t="inlineStr">
+        <is>
+          <t>HK_CHP_current</t>
+        </is>
+      </c>
+      <c r="AK447" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM447" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN447" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO447" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP447" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ447" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS447" t="inlineStr">
+        <is>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT447" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU447" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV447" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW447" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX447" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA447" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB447" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC447" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -58062,7 +67696,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -58145,7 +67779,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10">
@@ -58155,7 +67789,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>382</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11">
@@ -58175,7 +67809,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -58207,7 +67841,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3552</v>
+        <v>4402</v>
       </c>
     </row>
     <row r="16">
